--- a/440-préparation-release-concertation-230-ballot/ig/CodeSystem-tddui-identifier.xlsx
+++ b/440-préparation-release-concertation-230-ballot/ig/CodeSystem-tddui-identifier.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0</t>
+    <t>2.3.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-26T10:56:48+00:00</t>
+    <t>2026-02-26T11:09:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/440-préparation-release-concertation-230-ballot/ig/CodeSystem-tddui-identifier.xlsx
+++ b/440-préparation-release-concertation-230-ballot/ig/CodeSystem-tddui-identifier.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-26T11:09:50+00:00</t>
+    <t>2026-02-27T13:02:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/440-préparation-release-concertation-230-ballot/ig/CodeSystem-tddui-identifier.xlsx
+++ b/440-préparation-release-concertation-230-ballot/ig/CodeSystem-tddui-identifier.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-27T13:02:03+00:00</t>
+    <t>2026-03-02T09:38:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
